--- a/file/table/TSIG_CNLookupTable.xlsx
+++ b/file/table/TSIG_CNLookupTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30012"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HIDG\SHP\CN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.TSIG\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1ACB98-B826-4A3E-A87A-CE8B2F718928}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA62337-6A11-4E88-AA87-D06A8F596616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{6CDDA331-BFDF-49DD-B321-19D1E6DB5E99}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{6CDDA331-BFDF-49DD-B321-19D1E6DB5E99}"/>
   </bookViews>
   <sheets>
     <sheet name="CNLookupTable" sheetId="1" r:id="rId1"/>
@@ -260,9 +260,8 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
+      <name val="Segoe UI Light"/>
       <family val="2"/>
-      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="3">
@@ -349,7 +348,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -360,6 +359,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -405,9 +405,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -445,7 +445,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -551,7 +551,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -693,7 +693,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -702,13 +702,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{181ED00D-5749-4C70-A6E7-287A114CF37C}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="4" max="4" width="39.28515625" customWidth="1"/>
-    <col min="9" max="9" width="74.140625" customWidth="1"/>
+    <col min="1" max="3" width="10.6640625" style="4"/>
+    <col min="4" max="4" width="39.265625" style="4" customWidth="1"/>
+    <col min="5" max="8" width="10.6640625" style="4"/>
+    <col min="9" max="9" width="74.1328125" style="4" customWidth="1"/>
+    <col min="10" max="16384" width="10.6640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -737,641 +740,641 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+    <row r="2" spans="1:9" ht="33" x14ac:dyDescent="0.6">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7">
         <v>57</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="7">
         <v>73</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="7">
         <v>82</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="7">
         <v>86</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+    <row r="3" spans="1:9" ht="33" x14ac:dyDescent="0.6">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="7">
         <v>43</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="7">
         <v>65</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="7">
         <v>76</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="7">
         <v>82</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:9" ht="33" x14ac:dyDescent="0.6">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="7">
         <v>43</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="7">
         <v>65</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="7">
         <v>76</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="7">
         <v>82</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+    <row r="5" spans="1:9" ht="33" x14ac:dyDescent="0.6">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="7">
         <v>96</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="7">
         <v>96</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="7">
         <v>96</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="7">
         <v>96</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:9" ht="33" x14ac:dyDescent="0.6">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="7">
         <v>66</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="7">
         <v>74</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="7">
         <v>80</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="7">
         <v>82</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+    <row r="7" spans="1:9" ht="33" x14ac:dyDescent="0.6">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <v>66</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="7">
         <v>74</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="7">
         <v>80</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="7">
         <v>82</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+    <row r="8" spans="1:9" ht="33" x14ac:dyDescent="0.6">
+      <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="7">
         <v>67</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <v>78</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="7">
         <v>85</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="7">
         <v>89</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+    <row r="9" spans="1:9" ht="33" x14ac:dyDescent="0.6">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="7">
         <v>63</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <v>77</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="7">
         <v>85</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="7">
         <v>88</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+    <row r="10" spans="1:9" ht="33" x14ac:dyDescent="0.6">
+      <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <v>63</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <v>77</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="7">
         <v>85</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="7">
         <v>88</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+    <row r="11" spans="1:9" ht="33" x14ac:dyDescent="0.6">
+      <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="7">
         <v>63</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="7">
         <v>77</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="7">
         <v>85</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="7">
         <v>88</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+    <row r="12" spans="1:9" ht="33" x14ac:dyDescent="0.6">
+      <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <v>63</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="7">
         <v>77</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="7">
         <v>85</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="7">
         <v>88</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="7">
         <v>64</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="7">
         <v>75</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="7">
         <v>82</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="7">
         <v>85</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+    <row r="14" spans="1:9" ht="33" x14ac:dyDescent="0.6">
+      <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="7">
         <v>67</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="7">
         <v>78</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="7">
         <v>85</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="7">
         <v>89</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+    <row r="15" spans="1:9" ht="33" x14ac:dyDescent="0.6">
+      <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="7">
         <v>67</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="7">
         <v>78</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="7">
         <v>85</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="7">
         <v>89</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="7">
         <v>36</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="7">
         <v>60</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="7">
         <v>73</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="7">
         <v>79</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="7">
         <v>36</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="7">
         <v>60</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="7">
         <v>73</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="7">
         <v>79</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A18" s="7">
         <v>17</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="7">
         <v>36</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="7">
         <v>60</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="7">
         <v>73</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="7">
         <v>79</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="7">
         <v>30</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="7">
         <v>55</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="7">
         <v>70</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="7">
         <v>77</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="I19" s="8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+    <row r="20" spans="1:9" ht="33" x14ac:dyDescent="0.6">
+      <c r="A20" s="7">
         <v>19</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="7">
         <v>39</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="7">
         <v>61</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="7">
         <v>74</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="7">
         <v>80</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="I20" s="8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+    <row r="21" spans="1:9" ht="33" x14ac:dyDescent="0.6">
+      <c r="A21" s="7">
         <v>20</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="7">
         <v>49</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="7">
         <v>69</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="7">
         <v>79</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="7">
         <v>84</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="I21" s="8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+    <row r="22" spans="1:9" ht="33" x14ac:dyDescent="0.6">
+      <c r="A22" s="7">
         <v>21</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="7">
         <v>32</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="7">
         <v>58</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="7">
         <v>72</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="7">
         <v>79</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I22" s="8" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="10">
+    <row r="23" spans="1:9" ht="33" x14ac:dyDescent="0.6">
+      <c r="A23" s="11">
         <v>22</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="11">
         <v>77</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="11">
         <v>85</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="11">
         <v>90</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="11">
         <v>92</v>
       </c>
-      <c r="I23" s="12" t="s">
+      <c r="I23" s="13" t="s">
         <v>65</v>
       </c>
     </row>
